--- a/template_n.xlsx
+++ b/template_n.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thomas/Documents/GitHub/GvsP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30C98B1D-2CEF-D241-9308-DA2A23DED9BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08DDB409-6AF0-9549-B495-B83344986C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17480" xr2:uid="{664D0AB6-784C-1D41-9706-1EA9FD4AD4C9}"/>
   </bookViews>
@@ -38,19 +38,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
-    <t>Low Multicollinearity</t>
-  </si>
-  <si>
-    <t>High Multicollinearity</t>
-  </si>
-  <si>
     <t>n</t>
   </si>
   <si>
     <t xml:space="preserve"> f</t>
   </si>
   <si>
-    <t>Medium Multicollinearity</t>
+    <t>Low Pleiotropy</t>
+  </si>
+  <si>
+    <t>Medium Pleiotropy</t>
+  </si>
+  <si>
+    <t>High Pleiotropy</t>
   </si>
 </sst>
 </file>
@@ -625,17 +625,17 @@
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="12" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1" s="12"/>
       <c r="F1" s="12"/>
       <c r="G1" s="12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1" s="12"/>
       <c r="I1" s="12"/>
       <c r="J1" s="12" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K1" s="12"/>
       <c r="L1" s="12"/>
@@ -643,10 +643,10 @@
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
